--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024939</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">

--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -2164,7 +2164,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024939</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4654,12 +4654,12 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4879,12 +4879,12 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5179,12 +5179,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5554,12 +5554,12 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5704,12 +5704,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5779,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -2164,7 +2164,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6229,12 +6229,12 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6304,12 +6304,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6454,12 +6454,12 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
